--- a/Engagement/BCIO-engagement-hierarchy.xlsx
+++ b/Engagement/BCIO-engagement-hierarchy.xlsx
@@ -442,32 +442,32 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>subontology</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>informaldefinition</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>examples</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>informaldefinition</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>synonyms</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>subontology</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>crossreference</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>examples</t>
         </is>
       </c>
     </row>
@@ -524,13 +524,13 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BFO:0000002</t>
+          <t>BFO:0000003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>continuant</t>
+          <t>occurrent</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -542,21 +542,21 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>An entity that exists in full at any time in which it exists at all, persists through time while maintaining its identity and has no temporal parts.</t>
+          <t>An entity that has temporal parts and that happens, unfolds or develops through time.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BFO:0000031</t>
+          <t>BFO:0000008</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>generically dependent continuant</t>
+          <t>temporal region</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -565,16 +565,11 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IAO:0000030</t>
+          <t>BFO:0000038</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -582,7 +577,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>information content entity</t>
+          <t>one-dimensional temporal region</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -592,14 +587,22 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>A generically dependent continuant that is about some thing.</t>
-        </is>
-      </c>
+          <t>A one-dimensional temporal region is a temporal region that is extended.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IAO:0000027</t>
+          <t>BCIO:013035</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -608,7 +611,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>data item</t>
+          <t>BCI engagement period</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -617,38 +620,75 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>An information content entity that is intended to be a truthful statement about something (modulo, e.g., measurement precision or other systematic errors) and is constructed/acquired by a method which reliably tends to produce (approximately) truthful statements.</t>
-        </is>
-      </c>
+          <t>A temporal interval between the start of the first behavioural BCI engagement and the end of the last behavioural BCI engagement.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>The total period of time between the first and last occasion of engagement with the intervention content.</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>The video content was accessed for 6 weeks, the classes were attended for 12 months.</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Depending on how “BCI engagement period” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants attended the classes for at least 2 weeks, (2) maximum (e.g., participants attended the classes for up to 6 weeks, (3) mean (e.g., participants attended classes for 4 weeks on average) or (4) median (e.g., the median length participants attended classes was 4 weeks).</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BCIO:050521</t>
+          <t>BCIO:013030</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>BCI engagement period statistic</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>aggregate behavioural BCI engagement duration</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>A data item that is about a collection of BCI engagement periods.</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>A temporal interval that is the sum of the duration of behavioural BCI engagements for a BCI.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>A unit of time that describes the summed duration of all BCI engagement events.</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>90 minutes total app usage, 12 hours of counselling sessions</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>Describes the total duration of engagement in a BCI (e.g., all face-to-face sessions AND all telephone contacts), or the total duration of engagement in part of a BCI (e.g., all face-to-face sessions only). (A unit of time that describes the summed duration of all BCI engagement events.) 
+Depending on how “aggregate BCI engagement duration” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants talked to the therapist for at least 50 minutes in total across the sessions, (2) maximum (e.g., participants talked to the therapist for up to 4.5 hours in total across the sessions, (3) mean (e.g., participants talked with the therapist, on average, for 3 hours in total across the sessions) or (4) median (e.g., the median length of time participants talked with therapists in all their session was 3 hours).</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -657,188 +697,180 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BCIO:050528</t>
+          <t>BCIO:013025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>behavioural BCI engagement duration</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>maximum BCI engagement period</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>A BCI engagement period statistic that is the highest value from a collection of BCI engagement periods.</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>A temporal interval between the start and end of a behavioural BCI engagement.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>A unit of time that describes the length of an engagement event.</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>A 30-minute session, 1 hour spent 'logged in'</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>The class “BCI engagement duration” can be used multiple times to capture the frequency of different types of engagements, such as the frequency of engaging with social media or printed material. 
+Depending on how “BCI engagement duration” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants talked to the therapist for at least 10 minutes in each session, (2) maximum (e.g., participants talked to the therapist for up to 1 hour in each session, (3) mean (e.g., participants talked with the therapist for 45 minutes on average in each session) or (4) median (e.g., the median length of calls between participants and therapists was 42 minutes in each session).</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>The maximum period of intervention that participants engaged with.</t>
-        </is>
-      </c>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BCIO:050543</t>
+          <t>BCIO:050549</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>temporal reference point associated with behavioural BCI engagement</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>minimum BCI engagement period</t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>A BCI engagement period statistic that is the lowest value from a collection of BCI engagement periods.</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A time point against which behavioural BCI engagement is referenced.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>First engagement with an app (e.g., 2 weeks after app launch)</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>The minimum period of intervention that participants engaged with.</t>
-        </is>
-      </c>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BCIO:050533</t>
+          <t>BFO:0000015</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>mean BCI engagement period</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>A BCI engagement period statistic that is the average value calculated from a collection of BCI engagement periods.</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>The mean period of intervention  that participants engaged with.</t>
+          <t>p is a process = Def. p is an occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t. (axiom label in BFO2 Reference: [083-003])</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BCIO:050538</t>
+          <t>BCIO:040000</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>individual human activity</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>median BCI engagement period</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>A BCI engagement period statistic that is the central value of a collection of BCI engagement periods.</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>The median period of intervention that participants engaged with.</t>
+          <t>A process that is produced by a person.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCIO:050525</t>
+          <t>BCIO:050916</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>behavioural BCI engagement number statistic</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>participant engagement with intervention</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>A data item that is about a collection of behavioural BCI engagement contact event numbers.</t>
+          <t>An individual human activity of an intervention participant within one or more parts of the intervention.</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>The extend to which someone interacts with an intervention, including their cognitive, emotional and behavioural response (e.g., attending intervention session) to the intervention itself.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCIO:050542</t>
+          <t>BCIO:013000</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -846,36 +878,32 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>median behavioural BCI engagement number</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>participant engagement with behaviour change intervention</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement number statistic that is the central value of a collection of behavioural BCI engagement numbers.</t>
+          <t>Participant engagement with intervention, where the intervention focuses on changing behaviour.</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>The median number of intervention sessions attended by participants.</t>
-        </is>
-      </c>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCIO:050532</t>
+          <t>BCIO:013040</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -886,33 +914,39 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>maximum behavioural BCI engagement number</t>
+          <t>cognitive BCI engagement</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement number statistic that is the highest value from a collection of behavioural BCI engagement numbers.</t>
+          <t>Participant engagement with behaviour change intervention in which the engagement activity is a cognitive process.</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Paying attention or understanding an intervention’s content, thinking, forming, or changing beliefs about intervention</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>Describes engagement which can be demonstrated through reviewing, understanding, learning or recalling the intervention content. Cognitive processes entail the act of directing the mind to see, listen or understand.</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>The maximum number of intervention sessions attended by participants.</t>
-        </is>
-      </c>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCIO:050547</t>
+          <t>BCIO:013045</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -921,35 +955,45 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>minimum behavioural BCI engagement number</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>cognitive BCI engagement through attention</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement number statistic that is the lowest value from a collection of behavioural BCI engagement numbers.</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>A cognitive BCI engagement that involves attending.</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Paying attention to an intervention’s content</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Paying attention to certain images or information within the intervention</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>“Attending” is defined as “The process whereby relevant aspects of our mental experience are focused on specific targets.”</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>The minimum number of intervention sessions attended by participants.</t>
-        </is>
-      </c>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BCIO:050537</t>
+          <t>BCIO:013055</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -958,35 +1002,41 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>mean behavioural BCI engagement number</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>cognitive BCI engagement through judging</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement number statistic that is the average value calculated from a collection of behavioural BCI engagement numbers.</t>
+          <t>A cognitive BCI engagement that involves a judging process.</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Evaluations of usefulness, relevance usability or effectiveness.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>“Judging” is defined as “A &lt;mental process&gt; during which information is evaluated, the outcome of which is a belief or opinion.”</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>The mean number of intervention sessions attended by participants.</t>
-        </is>
-      </c>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BCIO:050522</t>
+          <t>BCIO:013050</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -994,23 +1044,32 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>aggregate behavioural BCI engagement duration statistic</t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>cognitive BCI engagement through comprehension</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>A data item that is about a collection of aggregate behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>A cognitive BCI engagement that involves comprehension.</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Comprehension of meaning, requirements or importance. Formal testing, providing feedback</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>“Comprehension” is defined as “A cognitive process that creates a representation of the meaning and significance of a communication, object, event or situation.”</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -1019,7 +1078,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BCIO:050529</t>
+          <t>BCIO:013060</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1030,33 +1089,44 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>maximum aggregate behavioural BCI engagement duration</t>
+          <t>emotional BCI engagement</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>An aggregate behavioural BCI engagement duration statistic that is the highest value from a collection of aggregate behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>Participant engagement with behaviour change intervention in which the engagement activity is an emotion process.</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Engagement through having or expressing feelings or emotions in relation to an intervention.</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Enjoying or liking the intervention</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>“Emotional BCI engagement” classes in the ontology are about how engagement is recorded or reported relevant to an individual’s response to the intervention content. Some interventions intend to elicit emotional responses as mechanisms of actions or outcomes, but these are not captured by the current class. 
+“Emotion process” is defined as “A mental process that is a synchronized aggregate of constituent mental processes including an appraisal process, which is valenced, has an object, and gives rise to an action tendency.”</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>The maximum duration of all intervention sessions attended by participants.</t>
-        </is>
-      </c>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BCIO:050544</t>
+          <t>BCIO:013065</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1065,35 +1135,41 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>minimum aggregate behavioural BCI engagement duration</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>emotional BCI engagement through enjoyment</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>An aggregate behavioural BCI engagement duration statistic that is the lowest value from a collection of aggregate behavioural BCI engagement durations.</t>
+          <t>Emotional BCI engagement that involves enjoyment.</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Experiencing pleasure through interacting/using the intervention (e.g., gamification).</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>“Enjoyment” is defined as “A positive emotion that is about an ongoing experience and reflects that the experience is being appraised as pleasurable.”</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>The minimum duration of all intervention sessions attended by participants.</t>
-        </is>
-      </c>
+      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BCIO:050539</t>
+          <t>BCIO:050527</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1102,35 +1178,36 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>median aggregate behavioural BCI engagement duration</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>emotional BCI engagement through mistrust</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>An aggregate behavioural BCI engagement duration statistic that is the central value of a collection of aggregate behavioural BCI engagement durations.</t>
+          <t>Emotional BCI engagement that involves mistrust.</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>“Mistrust” is defined as “A negative emotion involving feelings of suspicion or doubt regarding the honesty, fairness, or abilities of an entity (e.g., person, object, or situation).”</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>The median duration of all intervention sessions attended by participants.</t>
-        </is>
-      </c>
+      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BCIO:050534</t>
+          <t>BCIO:050526</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1139,35 +1216,36 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>mean aggregate behavioural BCI engagement duration</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>emotional BCI engagement through fear</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>An aggregate behavioural BCI engagement duration statistic that is the average value calculated from a collection of aggregate behavioural BCI engagement durations.</t>
+          <t>Emotional BCI engagement that involves fear.</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>“Fear” is defined as “A negative emotion that is aversive and characterised by feelings of threat and impending doom, and by an urge to get out of the situation.”</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>The mean duration of all intervention sessions attended by participants.</t>
-        </is>
-      </c>
+      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BCIO:050523</t>
+          <t>BCIO:013070</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1175,23 +1253,33 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>behavioural BCI engagement duration statistic</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>emotional BCI engagement through satisfaction</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>A data item that is about a collection of behavioural BCI engagement durations.</t>
+          <t>Emotional BCI engagement that involves satisfaction.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Experiencing satisfaction by fulfilling needs, expectations or wishes.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>“Satisfaction” is defined as “An emotion that is experienced when one's wishes, expectations or needs are fulfilled.”</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -1200,7 +1288,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BCIO:050540</t>
+          <t>BCIO:013075</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1209,35 +1297,43 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>median behavioural BCI engagement duration</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>emotional BCI engagement through interest</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement duration statistic that is the central value of a collection of behavioural BCI engagement durations.</t>
+          <t>Emotional BCI engagement that involves interest.</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Experiencing interest in the intervention by creating a desire to learn more.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>In the Emotion Ontology, “interest” is defined as “a positive emotion which motivates learning, exploration and curiosity. Feelings of interest are associated with the novelty and complexity of stimuli.” 
+“Emotional BCI engagement through interest” can have a cognitive component or be associated with “cognitive BCI engagement through attending” or “cognitive engagement through evaluation”, as emotion and cognitive processes are often related. For instance, participants rating the “informativeness” of an intervention would qualify as a “cognitive engagement through evaluation”. 
+The opposite of interest is boredom.</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>The median duration of intervention sessions attended by participants.</t>
-        </is>
-      </c>
+      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BCIO:050545</t>
+          <t>BCIO:013010</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1248,107 +1344,93 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>minimum behavioural BCI engagement duration</t>
+          <t>behavioural BCI engagement</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement duration statistic that is the lowest value from a collection of behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>Participant engagement with behaviour change intervention in which the engagement activity is a behaviour.</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Any behaviour performed to engage with an intervention and its content.</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Eye movements, body movements, meditation, attending an intervention session, using nicotine patches in a smoking cessation intervention, or online activity: attending, logging in, posting on a discussion board, reading content, mouse clicks, viewing, using tools, journaling</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>This is distinguished from engagement that involves thought processes.</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>The minimum duration of intervention sessions attended by participants.</t>
-        </is>
-      </c>
+      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BCIO:050535</t>
+          <t>OGMS:0000060</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>bodily process</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>mean behavioural BCI engagement duration</t>
-        </is>
-      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement duration statistic that is the average value calculated from a collection of behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>The mean duration of intervention sessions attended by participants.</t>
+          <t>A process in which at least one bodily component of an organism participates.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BCIO:050530</t>
+          <t>MF:0000020</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>mental process</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>maximum behavioural BCI engagement duration</t>
-        </is>
-      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement duration statistic that is the highest value from a collection of behavioural BCI engagement durations.</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>The maximum duration of intervention sessions attended by participants.</t>
+          <t>A &lt;bodily process&gt; that occurs in the brain, and that can of itself be conscious, or can give rise to a process that can of itself be conscious or can give rise to behaviour.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BCIO:013015</t>
+          <t>MF:0000008</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1358,7 +1440,7 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>number of behavioural BCI engagements</t>
+          <t>cognitive process</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -1366,32 +1448,27 @@
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>A data item that is about the number of times behavioural BCI engagement occurs.</t>
+          <t>A mental process that creates, modifies or has as participant some cognitive representation.</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Describes the total number of engagement events in a BCI (e.g., participants received 10 sessions face-to-face or by phone), or the number of engagement events related to part of a BCI (e.g., 10% of people participated in 6 face-to-face sessions and 4 phone sessions). 
-Depending on how “number of BCI engagements” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants joined at least 1 session), (2) maximum (e.g., only 10% of participants attended 5 sessions), (3) mean (e.g., participants joined 4 sessions on average) or (4) median (e.g., the median number of sessions participants attended was 4).</t>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Understanding, or thinking about something or forming or changing beliefs about something.</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>Number of: sessions attended, worksheets initiated, log ins, online posts, online responses. The amount of content viewed or the number of non-consecutive days an intervention was engaged with (e.g. the app was used on 20 days out of a possible 60 days).</t>
-        </is>
-      </c>
+      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BCIO:050524</t>
+          <t>BCIO:006110</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1399,32 +1476,32 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>behavioural BCI engagement frequency statistic</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>comprehension</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>A data item that is about a collection of behavioural BCI engagement frequencies.</t>
+          <t>A cognitive process that creates a representation of the meaning and significance of a communication, object, event or situation.</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BCIO:050531</t>
+          <t>MF:0000006</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1432,36 +1509,32 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>maximum behavioural BCI engagement frequency</t>
-        </is>
-      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>judging</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement frequency statistic that is the highest value from a collection of behavioural BCI engagement frequencies.</t>
+          <t>A mental process during which information is evaluated, the outcome of which is a belief or opinion.</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>The maximum frequency of intervention sessions attended by participants.</t>
-        </is>
-      </c>
+      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BCIO:050541</t>
+          <t>MF:0000018</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1469,36 +1542,37 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>median behavioural BCI engagement frequency</t>
-        </is>
-      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>attending</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement frequency statistic that is the central value of a collection of behavioural BCI engagement frequencies.</t>
+          <t>the process whereby relevant aspects of our mental experience are focused on specific targets</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Focusing on particular internal or external stimuli.</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>The median frequency of intervention sessions attended by participants.</t>
-        </is>
-      </c>
+      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BCIO:050546</t>
+          <t>MFOEM:000195</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1506,36 +1580,24 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>minimum behavioural BCI engagement frequency</t>
-        </is>
-      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>affective process</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement frequency statistic that is the lowest value from a collection of behavioural BCI engagement frequencies.</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>The minimum frequency of intervention sessions attended by participants.</t>
+          <t>A mental process that has positive or negative valence.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BCIO:050536</t>
+          <t>MFOEM:000001</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1546,33 +1608,29 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>mean behavioural BCI engagement frequency</t>
+          <t>emotion process</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>A behavioural BCI engagement frequency statistic that is the average value calculated from a collection of behavioural BCI engagement frequencies.</t>
+          <t>An affective process that is a synchronized aggregate of constituent mental processes, including an appraisal process, which is valenced, has an object, and gives rise to an action tendency.</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>The mean frequency of intervention sessions attended by participants.</t>
-        </is>
-      </c>
+      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BCIO:013020</t>
+          <t>MFOEM:000169</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1580,156 +1638,151 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>behavioural BCI engagement frequency</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>satisfaction</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>A data item that is about the number of times behavioural BCI engagement occurs within a unit of time.</t>
+          <t>An emotion that is experienced when one's wishes, expectations or needs are fulfilled.</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Describes the frequency of BCI engagement in a BCI (e.g., participants had weekly contact), or the frequency of engagement in part of a BCI (e.g., participants received face-to-face contact once a month). 
-The class “BCI engagement frequency” can be used to capture the frequency of different types of engagement, such as the frequency of engaging with social media or printed material. 
-Depending on how “BCI engagement frequency” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants joined at least 1 session every week), (2) maximum (e.g., only 10% of participants attended 5 sessions every week), (3) mean (e.g., participants joined 4 sessions per week on average) or (4) median (e.g., the median number of sessions participants attended was 4 per week).</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>Hourly, daily, weekly or monthly encounters.</t>
-        </is>
-      </c>
+      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BFO:0000003</t>
+          <t>MFOEM:000026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>occurrent</t>
-        </is>
-      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>An entity that has temporal parts and that happens, unfolds or develops through time.</t>
-        </is>
-      </c>
+          <t>A negative emotion that is aversive and characterised by feelings of threat and impending doom, and by an urge to get out of the situation.</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BFO:0000015</t>
+          <t>MFOEM:000033</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>process</t>
-        </is>
-      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>p is a process = Def. p is an occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t. (axiom label in BFO2 Reference: [083-003])</t>
-        </is>
-      </c>
+          <t>Interest is a positive emotion which motivates learning, exploration and curiosity. Feelings of interest are associated with the novelty and complexity of stimuli</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BCIO:040000</t>
+          <t>MFOEM:000225</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>individual human activity</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>mistrust</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>A process that is produced by a person.</t>
-        </is>
-      </c>
+          <t>A negative emotion involving feelings of suspicion or doubt regarding the honesty, fairness, or abilities of an entity (e.g., person, object, or situation).</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BCIO:050916</t>
+          <t>MFOEM:000042</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>participant engagement with intervention</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>happiness</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>An individual human activity of an intervention participant within one or more parts of the intervention.</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>The extend to which someone interacts with an intervention, including their cognitive, emotional and behavioural response (e.g., attending intervention session) to the intervention itself.</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
+          <t>A positive emotion which is experienced in reaction to a positive experience or event. [Source: OCEAS]</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BCIO:013000</t>
+          <t>MFOEM:000218</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1737,208 +1790,132 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>participant engagement with behaviour change intervention</t>
-        </is>
-      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Genuss</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Participant engagement with intervention, where the intervention focuses on changing behaviour.</t>
+          <t>A positive emotion that is about an ongoing experience and reflects that the experience is being appraised as pleasurable</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BCIO:013010</t>
+          <t>BFO:0000002</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>continuant</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>behavioural BCI engagement</t>
-        </is>
-      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Participant engagement with behaviour change intervention in which the engagement activity is a behaviour.</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>This is distinguished from engagement that involves thought processes.</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>Any behaviour performed to engage with an intervention and its content.</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>Eye movements, body movements, meditation, attending an intervention session, using nicotine patches in a smoking cessation intervention, or online activity: attending, logging in, posting on a discussion board, reading content, mouse clicks, viewing, using tools, journaling</t>
+          <t>An entity that exists in full at any time in which it exists at all, persists through time while maintaining its identity and has no temporal parts.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BCIO:013060</t>
+          <t>BFO:0000031</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>generically dependent continuant</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>emotional BCI engagement</t>
-        </is>
-      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Participant engagement with behaviour change intervention in which the engagement activity is an emotion process.</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>“Emotional BCI engagement” classes in the ontology are about how engagement is recorded or reported relevant to an individual’s response to the intervention content. Some interventions intend to elicit emotional responses as mechanisms of actions or outcomes, but these are not captured by the current class. 
-“Emotion process” is defined as “A mental process that is a synchronized aggregate of constituent mental processes including an appraisal process, which is valenced, has an object, and gives rise to an action tendency.”</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Engagement through having or expressing feelings or emotions in relation to an intervention.</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>Enjoying or liking the intervention</t>
+          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BCIO:013070</t>
+          <t>IAO:0000030</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>information content entity</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>emotional BCI engagement through satisfaction</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Emotional BCI engagement that involves satisfaction.</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>“Satisfaction” is defined as “An emotion that is experienced when one's wishes, expectations or needs are fulfilled.”</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>Experiencing satisfaction by fulfilling needs, expectations or wishes.</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
+          <t>A generically dependent continuant that is about some thing.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BCIO:050527</t>
+          <t>IAO:0000027</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>data entity</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>emotional BCI engagement through mistrust</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Emotional BCI engagement that involves mistrust.</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>“Mistrust” is defined as “A negative emotion involving feelings of suspicion or doubt regarding the honesty, fairness, or abilities of an entity (e.g., person, object, or situation).”</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
+          <t>An information content entity that is intended to be one or more truthful statement(s) about something (modulo, e.g., measurement precision or other systematic errors) and is constructed/acquired by a method which reliably tends to produce (approximately) truthful statements.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BCIO:013065</t>
+          <t>BCIO:050524</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1946,42 +1923,32 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>behavioural BCI engagement frequency statistic</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>emotional BCI engagement through enjoyment</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Emotional BCI engagement that involves enjoyment.</t>
+          <t>A data item that is about a collection of behavioural BCI engagement frequencies.</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>“Enjoyment” is defined as “A positive emotion that is about an ongoing experience and reflects that the experience is being appraised as pleasurable.”</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>Experiencing pleasure through interacting/using the intervention (e.g., gamification).</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BCIO:050526</t>
+          <t>BCIO:050531</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1990,27 +1957,26 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>emotional BCI engagement through fear</t>
-        </is>
-      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>maximum behavioural BCI engagement frequency</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Emotional BCI engagement that involves fear.</t>
+          <t>A behavioural BCI engagement frequency statistic that is the highest value from a collection of behavioural BCI engagement frequencies.</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>“Fear” is defined as “A negative emotion that is aversive and characterised by feelings of threat and impending doom, and by an urge to get out of the situation.”</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>The maximum frequency of intervention sessions attended by participants.</t>
         </is>
       </c>
       <c r="P45" t="inlineStr"/>
@@ -2019,7 +1985,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BCIO:013075</t>
+          <t>BCIO:050536</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2028,34 +1994,26 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>emotional BCI engagement through interest</t>
-        </is>
-      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>mean behavioural BCI engagement frequency</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Emotional BCI engagement that involves interest.</t>
+          <t>A behavioural BCI engagement frequency statistic that is the average value calculated from a collection of behavioural BCI engagement frequencies.</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>In the Emotion Ontology, “interest” is defined as “a positive emotion which motivates learning, exploration and curiosity. Feelings of interest are associated with the novelty and complexity of stimuli.” 
-“Emotional BCI engagement through interest” can have a cognitive component or be associated with “cognitive BCI engagement through attending” or “cognitive engagement through evaluation”, as emotion and cognitive processes are often related. For instance, participants rating the “informativeness” of an intervention would qualify as a “cognitive engagement through evaluation”. 
-The opposite of interest is boredom.</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Experiencing interest in the intervention by creating a desire to learn more.</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>The mean frequency of intervention sessions attended by participants.</t>
         </is>
       </c>
       <c r="P46" t="inlineStr"/>
@@ -2064,7 +2022,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BCIO:013040</t>
+          <t>BCIO:050541</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2075,30 +2033,24 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>cognitive BCI engagement</t>
+          <t>median behavioural BCI engagement frequency</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Participant engagement with behaviour change intervention in which the engagement activity is a cognitive process.</t>
+          <t>A behavioural BCI engagement frequency statistic that is the central value of a collection of behavioural BCI engagement frequencies.</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Describes engagement which can be demonstrated through reviewing, understanding, learning or recalling the intervention content. Cognitive processes entail the act of directing the mind to see, listen or understand.</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>Paying attention or understanding an intervention’s content, thinking, forming, or changing beliefs about intervention</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>The median frequency of intervention sessions attended by participants.</t>
         </is>
       </c>
       <c r="P47" t="inlineStr"/>
@@ -2107,7 +2059,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BCIO:013055</t>
+          <t>BCIO:050546</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2116,32 +2068,26 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>cognitive BCI engagement through judging</t>
-        </is>
-      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>minimum behavioural BCI engagement frequency</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>A cognitive BCI engagement that involves a judging process.</t>
+          <t>A behavioural BCI engagement frequency statistic that is the lowest value from a collection of behavioural BCI engagement frequencies.</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>“Judging” is defined as “A &lt;mental process&gt; during which information is evaluated, the outcome of which is a belief or opinion.”</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>Evaluations of usefulness, relevance usability or effectiveness.</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>The minimum frequency of intervention sessions attended by participants.</t>
         </is>
       </c>
       <c r="P48" t="inlineStr"/>
@@ -2150,7 +2096,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BCIO:013050</t>
+          <t>BCIO:050523</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2158,41 +2104,32 @@
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>behavioural BCI engagement duration statistic</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>cognitive BCI engagement through comprehension</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>A cognitive BCI engagement that involves comprehension.</t>
+          <t>A data item that is about a collection of behavioural BCI engagement durations.</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>“Comprehension” is defined as “A cognitive process that creates a representation of the meaning and significance of a communication, object, event or situation.”</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>Comprehension of meaning, requirements or importance. Formal testing, providing feedback</t>
-        </is>
-      </c>
+      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BCIO:013045</t>
+          <t>BCIO:050535</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2201,95 +2138,109 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>cognitive BCI engagement through attention</t>
-        </is>
-      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>mean behavioural BCI engagement duration</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>A cognitive BCI engagement that involves attending.</t>
+          <t>A behavioural BCI engagement duration statistic that is the average value calculated from a collection of behavioural BCI engagement durations.</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>“Attending” is defined as “The process whereby relevant aspects of our mental experience are focused on specific targets.”</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>Paying attention to an intervention’s content</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>The mean duration of intervention sessions attended by participants.</t>
         </is>
       </c>
       <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>Paying attention to certain images or information within the intervention</t>
-        </is>
-      </c>
+      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>OGMS:0000060</t>
+          <t>BCIO:050540</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>bodily process</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>median behavioural BCI engagement duration</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>A &lt;process&gt; in which at least one bodily component of an organism participates.</t>
-        </is>
-      </c>
+          <t>A behavioural BCI engagement duration statistic that is the central value of a collection of behavioural BCI engagement durations.</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>The median duration of intervention sessions attended by participants.</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MF:0000020</t>
+          <t>BCIO:050530</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>mental process</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>maximum behavioural BCI engagement duration</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>A bodily process that occurs in the brain, and that can of itself be conscious, or can give rise to a process that can of itself be conscious or can give rise to behaviour.</t>
-        </is>
-      </c>
+          <t>A behavioural BCI engagement duration statistic that is the highest value from a collection of behavioural BCI engagement durations.</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>The maximum duration of intervention sessions attended by participants.</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MFOEM:000195</t>
+          <t>BCIO:050545</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2297,24 +2248,36 @@
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>affective process</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>minimum behavioural BCI engagement duration</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>A &lt;mental process&gt; that has positive or negative valence.</t>
-        </is>
-      </c>
+          <t>A behavioural BCI engagement duration statistic that is the lowest value from a collection of behavioural BCI engagement durations.</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>The minimum duration of intervention sessions attended by participants.</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MFOEM:000001</t>
+          <t>BCIO:050521</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2322,32 +2285,32 @@
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>emotion process</t>
-        </is>
-      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>BCI engagement period statistic</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>An affective process that is a synchronized aggregate of constituent mental processes, including an appraisal process, which is valenced, has an object, and gives rise to an action tendency.</t>
+          <t>A data item that is about a collection of BCI engagement periods.</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MFOEM:000225</t>
+          <t>BCIO:050533</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2356,22 +2319,26 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>mistrust</t>
-        </is>
-      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>mean BCI engagement period</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>A negative emotion involving feelings of suspicion or doubt regarding the honesty, fairness, or abilities of an entity (e.g., person, object, or situation).</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A BCI engagement period statistic that is the average value calculated from a collection of BCI engagement periods.</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>The mean period of intervention  that participants engaged with.</t>
         </is>
       </c>
       <c r="P55" t="inlineStr"/>
@@ -2380,7 +2347,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MFOEM:000042</t>
+          <t>BCIO:050543</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2389,23 +2356,35 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>happiness</t>
-        </is>
-      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>minimum BCI engagement period</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>A positive emotion which is experienced in reaction to a positive experience or event. [Source: OCEAS]</t>
-        </is>
-      </c>
+          <t>A BCI engagement period statistic that is the lowest value from a collection of BCI engagement periods.</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>The minimum period of intervention that participants engaged with.</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MFOEM:000218</t>
+          <t>BCIO:050538</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2414,22 +2393,26 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>median BCI engagement period</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>enjoyment</t>
-        </is>
-      </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>A positive emotion that is about an ongoing experience and reflects that the experience is being appraised as pleasurable</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A BCI engagement period statistic that is the central value of a collection of BCI engagement periods.</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>The median period of intervention that participants engaged with.</t>
         </is>
       </c>
       <c r="P57" t="inlineStr"/>
@@ -2438,7 +2421,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MFOEM:000169</t>
+          <t>BCIO:050528</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2447,22 +2430,26 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>satisfaction</t>
-        </is>
-      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>maximum BCI engagement period</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>An emotion that is experienced when one's wishes, expectations or needs are fulfilled.</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A BCI engagement period statistic that is the highest value from a collection of BCI engagement periods.</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>The maximum period of intervention that participants engaged with.</t>
         </is>
       </c>
       <c r="P58" t="inlineStr"/>
@@ -2471,7 +2458,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MFOEM:000026</t>
+          <t>BCIO:050522</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2479,17 +2466,22 @@
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>aggregate behavioural BCI engagement duration statistic</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>fear</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>A negative emotion that is aversive and characterised by feelings of threat and impending doom, and by an urge to get out of the situation.</t>
+          <t>A data item that is about a collection of aggregate behavioural BCI engagement durations.</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -2499,7 +2491,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MFOEM:000033</t>
+          <t>BCIO:050534</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2508,22 +2500,26 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>interest</t>
-        </is>
-      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>mean aggregate behavioural BCI engagement duration</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Interest is a positive emotion which motivates learning, exploration and curiosity. Feelings of interest are associated with the novelty and complexity of stimuli</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>An aggregate behavioural BCI engagement duration statistic that is the average value calculated from a collection of aggregate behavioural BCI engagement durations.</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>The mean duration of all intervention sessions attended by participants.</t>
         </is>
       </c>
       <c r="P60" t="inlineStr"/>
@@ -2532,7 +2528,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MF:0000018</t>
+          <t>BCIO:050529</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2540,28 +2536,27 @@
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>attending</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>maximum aggregate behavioural BCI engagement duration</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>the process whereby relevant aspects of our mental experience are focused on specific targets</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>Focusing on particular internal or external stimuli.</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>An aggregate behavioural BCI engagement duration statistic that is the highest value from a collection of aggregate behavioural BCI engagement durations.</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>The maximum duration of all intervention sessions attended by participants.</t>
         </is>
       </c>
       <c r="P61" t="inlineStr"/>
@@ -2570,7 +2565,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MF:0000008</t>
+          <t>BCIO:050539</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2578,28 +2573,27 @@
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>cognitive process</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>median aggregate behavioural BCI engagement duration</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>A mental process that creates, modifies or has as participant some cognitive representation.</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>Understanding, or thinking about something or forming or changing beliefs about something.</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>An aggregate behavioural BCI engagement duration statistic that is the central value of a collection of aggregate behavioural BCI engagement durations.</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>The median duration of all intervention sessions attended by participants.</t>
         </is>
       </c>
       <c r="P62" t="inlineStr"/>
@@ -2608,7 +2602,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BCIO:006110</t>
+          <t>BCIO:050544</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2619,20 +2613,24 @@
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>comprehension</t>
+          <t>minimum aggregate behavioural BCI engagement duration</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>A cognitive process that creates a representation of the meaning and significance of a communication, object, event or situation.</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>An aggregate behavioural BCI engagement duration statistic that is the lowest value from a collection of aggregate behavioural BCI engagement durations.</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>The minimum duration of all intervention sessions attended by participants.</t>
         </is>
       </c>
       <c r="P63" t="inlineStr"/>
@@ -2641,7 +2639,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MF:0000006</t>
+          <t>BCIO:013015</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2651,7 +2649,7 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>judging</t>
+          <t>number of behavioural BCI engagements</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
@@ -2659,13 +2657,23 @@
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>A mental process during which information is evaluated, the outcome of which is a belief or opinion.</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
+          <t>A data item that is about the number of times behavioural BCI engagement occurs.</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Number of: sessions attended, worksheets initiated, log ins, online posts, online responses. The amount of content viewed or the number of non-consecutive days an intervention was engaged with (e.g. the app was used on 20 days out of a possible 60 days).</t>
+        </is>
+      </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>Describes the total number of engagement events in a BCI (e.g., participants received 10 sessions face-to-face or by phone), or the number of engagement events related to part of a BCI (e.g., 10% of people participated in 6 face-to-face sessions and 4 phone sessions). 
+Depending on how “number of BCI engagements” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants joined at least 1 session), (2) maximum (e.g., only 10% of participants attended 5 sessions), (3) mean (e.g., participants joined 4 sessions on average) or (4) median (e.g., the median number of sessions participants attended was 4).</t>
         </is>
       </c>
       <c r="P64" t="inlineStr"/>
@@ -2674,235 +2682,227 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BFO:0000008</t>
+          <t>BCIO:013020</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>temporal region</t>
-        </is>
-      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>behavioural BCI engagement frequency</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>A data item that is about the number of times behavioural BCI engagement occurs within a unit of time.</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Hourly, daily, weekly or monthly encounters.</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Describes the frequency of BCI engagement in a BCI (e.g., participants had weekly contact), or the frequency of engagement in part of a BCI (e.g., participants received face-to-face contact once a month). 
+The class “BCI engagement frequency” can be used to capture the frequency of different types of engagement, such as the frequency of engaging with social media or printed material. 
+Depending on how “BCI engagement frequency” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants joined at least 1 session every week), (2) maximum (e.g., only 10% of participants attended 5 sessions every week), (3) mean (e.g., participants joined 4 sessions per week on average) or (4) median (e.g., the median number of sessions participants attended was 4 per week).</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BFO:0000038</t>
+          <t>BCIO:050525</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>one-dimensional temporal region</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>behavioural BCI engagement number statistic</t>
+        </is>
+      </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>A one-dimensional temporal region is a temporal region that is extended.</t>
+          <t>A data item that is about a collection of behavioural BCI engagement contact event numbers.</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BCIO:013030</t>
+          <t>BCIO:050547</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>aggregate behavioural BCI engagement duration</t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>minimum behavioural BCI engagement number</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>A temporal interval that is the sum of the duration of behavioural BCI engagements for a BCI.</t>
+          <t>A behavioural BCI engagement number statistic that is the lowest value from a collection of behavioural BCI engagement numbers.</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Describes the total duration of engagement in a BCI (e.g., all face-to-face sessions AND all telephone contacts), or the total duration of engagement in part of a BCI (e.g., all face-to-face sessions only). (A unit of time that describes the summed duration of all BCI engagement events.) 
-Depending on how “aggregate BCI engagement duration” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants talked to the therapist for at least 50 minutes in total across the sessions, (2) maximum (e.g., participants talked to the therapist for up to 4.5 hours in total across the sessions, (3) mean (e.g., participants talked with the therapist, on average, for 3 hours in total across the sessions) or (4) median (e.g., the median length of time participants talked with therapists in all their session was 3 hours).</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>A unit of time that describes the summed duration of all BCI engagement events.</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>The minimum number of intervention sessions attended by participants.</t>
         </is>
       </c>
       <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>90 minutes total app usage, 12 hours of counselling sessions</t>
-        </is>
-      </c>
+      <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BCIO:013025</t>
+          <t>BCIO:050542</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>behavioural BCI engagement duration</t>
-        </is>
-      </c>
+      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>median behavioural BCI engagement number</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
-          <t>A temporal interval between the start and end of a behavioural BCI engagement.</t>
+          <t>A behavioural BCI engagement number statistic that is the central value of a collection of behavioural BCI engagement numbers.</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>The class “BCI engagement duration” can be used multiple times to capture the frequency of different types of engagements, such as the frequency of engaging with social media or printed material. 
-Depending on how “BCI engagement duration” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants talked to the therapist for at least 10 minutes in each session, (2) maximum (e.g., participants talked to the therapist for up to 1 hour in each session, (3) mean (e.g., participants talked with the therapist for 45 minutes on average in each session) or (4) median (e.g., the median length of calls between participants and therapists was 42 minutes in each session).</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>A unit of time that describes the length of an engagement event.</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>The median number of intervention sessions attended by participants.</t>
         </is>
       </c>
       <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>A 30-minute session, 1 hour spent 'logged in'</t>
-        </is>
-      </c>
+      <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BCIO:013035</t>
+          <t>BCIO:050537</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>BCI engagement period</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>mean behavioural BCI engagement number</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>A temporal interval between the start of the first behavioural BCI engagement and the end of the last behavioural BCI engagement.</t>
+          <t>A behavioural BCI engagement number statistic that is the average value calculated from a collection of behavioural BCI engagement numbers.</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Depending on how “BCI engagement period” is reported in interventions, it can be annotated with different data items, e.g. (1) minimum (e.g., all participants attended the classes for at least 2 weeks, (2) maximum (e.g., participants attended the classes for up to 6 weeks, (3) mean (e.g., participants attended classes for 4 weeks on average) or (4) median (e.g., the median length participants attended classes was 4 weeks).</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>The total period of time between the first and last occasion of engagement with the intervention content.</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>The mean number of intervention sessions attended by participants.</t>
         </is>
       </c>
       <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>The video content was accessed for 6 weeks, the classes were attended for 12 months.</t>
-        </is>
-      </c>
+      <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BCIO:050549</t>
+          <t>BCIO:050532</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>temporal reference point associated with behavioural BCI engagement</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>maximum behavioural BCI engagement number</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>A time point against which behavioural BCI engagement is referenced.</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>Engagement</t>
+          <t>A behavioural BCI engagement number statistic that is the highest value from a collection of behavioural BCI engagement numbers.</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>The maximum number of intervention sessions attended by participants.</t>
         </is>
       </c>
       <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>First engagement with an app (e.g., 2 weeks after app launch)</t>
-        </is>
-      </c>
+      <c r="Q70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
